--- a/artfynd/A 33486-2022 artfynd.xlsx
+++ b/artfynd/A 33486-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,6 +791,125 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131289202</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Svinömyren, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>450476</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6256348</v>
+      </c>
+      <c r="S3" t="n">
+        <v>98</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Loshult</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jonas Nilsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jonas Nilsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33486-2022 artfynd.xlsx
+++ b/artfynd/A 33486-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131242526</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>131289202</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33486-2022 artfynd.xlsx
+++ b/artfynd/A 33486-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131242526</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>131289202</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33486-2022 artfynd.xlsx
+++ b/artfynd/A 33486-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131242526</v>
+        <v>131289202</v>
       </c>
       <c r="B2" t="n">
-        <v>57728</v>
+        <v>57729</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,17 +718,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svinömyren, Svinön, Sk</t>
+          <t>Svinömyren, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450501</v>
+        <v>450476</v>
       </c>
       <c r="R2" t="n">
-        <v>6256400</v>
+        <v>6256348</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,22 +782,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Calner</t>
+          <t>Jonas Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Calner, Jukka Valtonen</t>
+          <t>Jonas Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131289202</v>
+        <v>131242526</v>
       </c>
       <c r="B3" t="n">
-        <v>57728</v>
+        <v>57729</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,17 +837,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svinömyren, Sk</t>
+          <t>Svinömyren, Svinön, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450476</v>
+        <v>450501</v>
       </c>
       <c r="R3" t="n">
-        <v>6256348</v>
+        <v>6256400</v>
       </c>
       <c r="S3" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,12 +901,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jonas Nilsson</t>
+          <t>Mikael Calner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jonas Nilsson</t>
+          <t>Mikael Calner, Jukka Valtonen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 33486-2022 artfynd.xlsx
+++ b/artfynd/A 33486-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131289202</v>
       </c>
       <c r="B2" t="n">
-        <v>57729</v>
+        <v>57732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>131242526</v>
       </c>
       <c r="B3" t="n">
-        <v>57729</v>
+        <v>57732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33486-2022 artfynd.xlsx
+++ b/artfynd/A 33486-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131289202</v>
       </c>
       <c r="B2" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>131242526</v>
       </c>
       <c r="B3" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33486-2022 artfynd.xlsx
+++ b/artfynd/A 33486-2022 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131289202</v>
+        <v>131242526</v>
       </c>
       <c r="B2" t="n">
-        <v>57745</v>
+        <v>57794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -718,17 +718,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svinömyren, Sk</t>
+          <t>Svinömyren, Svinön, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450476</v>
+        <v>450501</v>
       </c>
       <c r="R2" t="n">
-        <v>6256348</v>
+        <v>6256400</v>
       </c>
       <c r="S2" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,26 +782,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas Nilsson</t>
+          <t>Mikael Calner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Nilsson</t>
+          <t>Mikael Calner, Jukka Valtonen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131242526</v>
+        <v>131289202</v>
       </c>
       <c r="B3" t="n">
-        <v>57755</v>
+        <v>57794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -837,17 +837,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svinömyren, Svinön, Sk</t>
+          <t>Svinömyren, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450501</v>
+        <v>450476</v>
       </c>
       <c r="R3" t="n">
-        <v>6256400</v>
+        <v>6256348</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,12 +901,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Calner</t>
+          <t>Jonas Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Calner, Jukka Valtonen</t>
+          <t>Jonas Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
